--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="294">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,10 +319,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -342,6 +349,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -419,9 +429,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -442,6 +449,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -505,6 +522,9 @@
     <t>Status of the supply request.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -538,6 +558,9 @@
   </si>
   <si>
     <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>example</t>
@@ -627,6 +650,16 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -665,9 +698,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.parameter.extension</t>
   </si>
   <si>
@@ -795,6 +825,13 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1234,7 +1271,7 @@
     <col min="26" max="26" width="44.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1689,10 +1726,10 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1701,7 +1738,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1709,10 +1746,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1735,16 +1772,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1794,7 +1831,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1803,10 +1840,10 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -1815,7 +1852,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -1823,10 +1860,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1849,16 +1886,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1884,13 +1921,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1908,7 +1945,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1917,10 +1954,10 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -1929,7 +1966,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -1937,14 +1974,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1963,16 +2000,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2022,7 +2059,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2031,10 +2068,10 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2043,7 +2080,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2051,14 +2088,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2077,16 +2114,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2136,7 +2173,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2157,7 +2194,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2165,14 +2202,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2191,16 +2228,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2238,19 +2275,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2259,10 +2296,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2271,7 +2308,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2279,14 +2316,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2305,19 +2342,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2354,19 +2391,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2375,10 +2412,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2387,7 +2424,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2395,10 +2432,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2421,19 +2458,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2482,7 +2519,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2491,30 +2528,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2537,15 +2574,17 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2570,13 +2609,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2594,7 +2633,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2603,34 +2642,34 @@
         <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2649,15 +2688,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2682,31 +2723,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2715,30 +2756,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2761,21 +2802,23 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -2796,13 +2839,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -2820,7 +2863,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2829,30 +2872,30 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2875,16 +2918,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2895,7 +2938,7 @@
         <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>77</v>
@@ -2910,13 +2953,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2934,7 +2977,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -2943,19 +2986,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2963,10 +3006,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2989,15 +3032,17 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3046,7 +3091,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3055,19 +3100,19 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3075,10 +3120,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3101,13 +3146,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3158,7 +3203,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3167,30 +3212,30 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3213,13 +3258,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3270,7 +3315,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3291,7 +3336,7 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3299,14 +3344,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3325,16 +3370,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3372,19 +3417,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3393,10 +3438,10 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3405,7 +3450,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>102</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3413,14 +3458,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3439,19 +3484,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3500,7 +3545,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3509,10 +3554,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3521,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3529,10 +3574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3555,15 +3600,17 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3588,10 +3635,10 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>77</v>
@@ -3612,7 +3659,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3621,30 +3668,30 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3667,16 +3714,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3726,7 +3773,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3735,34 +3782,34 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3781,13 +3828,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3838,7 +3885,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3847,34 +3894,34 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3893,13 +3940,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3950,7 +3997,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3959,34 +4006,34 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4005,15 +4052,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4062,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4071,34 +4120,34 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4117,15 +4166,17 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4174,7 +4225,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4183,30 +4234,30 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4229,15 +4280,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4262,13 +4315,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4286,7 +4339,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4295,30 +4348,30 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4341,15 +4394,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4398,7 +4453,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4407,30 +4462,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4453,15 +4508,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4510,7 +4567,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4519,19 +4576,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4539,10 +4596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4565,15 +4622,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4622,7 +4681,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4631,19 +4690,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,17 +319,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -349,9 +342,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -429,6 +419,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -449,16 +442,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -522,9 +505,6 @@
     <t>Status of the supply request.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -558,9 +538,6 @@
   </si>
   <si>
     <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>example</t>
@@ -650,16 +627,6 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -698,6 +665,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyRequest.parameter.extension</t>
   </si>
   <si>
@@ -825,13 +795,6 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1271,7 +1234,7 @@
     <col min="26" max="26" width="44.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1726,11 +1689,11 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
@@ -1738,7 +1701,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1746,10 +1709,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1772,16 +1735,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1831,7 +1794,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1840,11 +1803,11 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
@@ -1852,7 +1815,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -1860,10 +1823,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1886,16 +1849,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1921,31 +1884,31 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1954,11 +1917,11 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
@@ -1966,7 +1929,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -1974,14 +1937,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2000,16 +1963,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2059,7 +2022,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2068,11 +2031,11 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
@@ -2080,7 +2043,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2088,14 +2051,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2114,16 +2077,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2173,7 +2136,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2194,7 +2157,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2202,14 +2165,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2228,16 +2191,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2275,19 +2238,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2296,10 +2259,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2308,7 +2271,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2316,14 +2279,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2342,19 +2305,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2391,19 +2354,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2412,10 +2375,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2424,7 +2387,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2432,10 +2395,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2458,19 +2421,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2519,7 +2482,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2528,30 +2491,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2574,17 +2537,15 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2609,13 +2570,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2633,7 +2594,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2642,34 +2603,34 @@
         <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2688,17 +2649,15 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2723,13 +2682,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2747,7 +2706,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2756,30 +2715,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2802,23 +2761,21 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -2839,13 +2796,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -2863,7 +2820,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2872,30 +2829,30 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2918,16 +2875,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2938,7 +2895,7 @@
         <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>77</v>
@@ -2953,13 +2910,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2977,7 +2934,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -2986,19 +2943,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3006,10 +2963,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3032,17 +2989,15 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3091,7 +3046,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3100,19 +3055,19 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3120,10 +3075,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3146,13 +3101,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3203,7 +3158,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3212,30 +3167,30 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3258,13 +3213,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3315,7 +3270,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3336,7 +3291,7 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3344,14 +3299,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3370,16 +3325,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3417,19 +3372,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3438,10 +3393,10 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3450,7 +3405,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3458,14 +3413,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3484,19 +3439,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3545,7 +3500,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3554,10 +3509,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3566,7 +3521,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3574,10 +3529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3600,17 +3555,15 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3635,10 +3588,10 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>77</v>
@@ -3659,7 +3612,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3668,30 +3621,30 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3714,16 +3667,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3773,7 +3726,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3782,34 +3735,34 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3828,13 +3781,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3885,7 +3838,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3894,34 +3847,34 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3940,13 +3893,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3997,7 +3950,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4006,34 +3959,34 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4052,17 +4005,15 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4111,7 +4062,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4120,34 +4071,34 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4166,17 +4117,15 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4225,7 +4174,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4234,30 +4183,30 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AK26" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4280,17 +4229,15 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4315,13 +4262,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4339,7 +4286,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4348,30 +4295,30 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4394,17 +4341,15 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4453,7 +4398,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4462,30 +4407,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4508,17 +4453,15 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4567,7 +4510,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4576,19 +4519,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ29" t="s" s="2">
+      <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AK29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AM29" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4596,10 +4539,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4622,17 +4565,15 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4681,7 +4622,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4690,19 +4631,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ30" t="s" s="2">
+      <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-commande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="294">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,10 +319,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -342,6 +349,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -419,9 +429,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -442,6 +449,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -505,6 +522,9 @@
     <t>Status of the supply request.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -538,6 +558,9 @@
   </si>
   <si>
     <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>example</t>
@@ -627,6 +650,16 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -665,9 +698,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.parameter.extension</t>
   </si>
   <si>
@@ -795,6 +825,13 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1234,7 +1271,7 @@
     <col min="26" max="26" width="44.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1689,10 +1726,10 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1701,7 +1738,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1709,10 +1746,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1735,16 +1772,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1794,7 +1831,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1803,10 +1840,10 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -1815,7 +1852,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -1823,10 +1860,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1849,16 +1886,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1884,13 +1921,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1908,7 +1945,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1917,10 +1954,10 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -1929,7 +1966,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -1937,14 +1974,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1963,16 +2000,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2022,7 +2059,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2031,10 +2068,10 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2043,7 +2080,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2051,14 +2088,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2077,16 +2114,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2136,7 +2173,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2157,7 +2194,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2165,14 +2202,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2191,16 +2228,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2238,19 +2275,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2259,10 +2296,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2271,7 +2308,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2279,14 +2316,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2305,19 +2342,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2354,19 +2391,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2375,10 +2412,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2387,7 +2424,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2395,10 +2432,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2421,19 +2458,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2482,7 +2519,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2491,30 +2528,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2537,15 +2574,17 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2570,13 +2609,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2594,7 +2633,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2603,34 +2642,34 @@
         <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2649,15 +2688,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2682,31 +2723,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2715,30 +2756,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2761,21 +2802,23 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -2796,13 +2839,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -2820,7 +2863,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2829,30 +2872,30 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2875,16 +2918,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2895,7 +2938,7 @@
         <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>77</v>
@@ -2910,13 +2953,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2934,7 +2977,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -2943,19 +2986,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2963,10 +3006,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2989,15 +3032,17 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3046,7 +3091,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3055,19 +3100,19 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3075,10 +3120,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3101,13 +3146,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3158,7 +3203,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3167,30 +3212,30 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3213,13 +3258,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3270,7 +3315,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3291,7 +3336,7 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3299,14 +3344,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3325,16 +3370,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3372,19 +3417,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3393,10 +3438,10 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3405,7 +3450,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>102</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3413,14 +3458,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3439,19 +3484,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3500,7 +3545,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3509,10 +3554,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3521,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3529,10 +3574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3555,15 +3600,17 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3588,10 +3635,10 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>77</v>
@@ -3612,7 +3659,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3621,30 +3668,30 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3667,16 +3714,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3726,7 +3773,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3735,34 +3782,34 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3781,13 +3828,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3838,7 +3885,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3847,34 +3894,34 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3893,13 +3940,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3950,7 +3997,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3959,34 +4006,34 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4005,15 +4052,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4062,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4071,34 +4120,34 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4117,15 +4166,17 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4174,7 +4225,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4183,30 +4234,30 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4229,15 +4280,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4262,13 +4315,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4286,7 +4339,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4295,30 +4348,30 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4341,15 +4394,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4398,7 +4453,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4407,30 +4462,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4453,15 +4508,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4510,7 +4567,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4519,19 +4576,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4539,10 +4596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4565,15 +4622,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4622,7 +4681,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4631,19 +4690,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
